--- a/information_forms/032_ethical_advisory_panel_application_form--information_forms.xlsx
+++ b/information_forms/032_ethical_advisory_panel_application_form--information_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
